--- a/output/2026-09-08_18_Croazia_Sisacko-moslavacka_Cleaning.xlsx
+++ b/output/2026-09-08_18_Croazia_Sisacko-moslavacka_Cleaning.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,6 @@
           <t>MAVING d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Sisak, Sisačko-moslavačka</t>
@@ -591,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
